--- a/data/processed_data/10V_3/contracciones_10V_3.xlsx
+++ b/data/processed_data/10V_3/contracciones_10V_3.xlsx
@@ -1965,7 +1965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH2"/>
+  <dimension ref="A1:CU2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2395,6 +2395,71 @@
         </is>
       </c>
       <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_cinetica_n_pulsos</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_n_con_cruce</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_n_medibles</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_reportable</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_ms</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_ic95_ms</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_cota_ms</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_n_con_cruce</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_n_medibles</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_reportable</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_ms</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_ic95_ms</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_cota_ms</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>forzada_periodo_origen</t>
         </is>
@@ -2676,7 +2741,50 @@
       <c r="CG2" t="n">
         <v>0.2623175892192328</v>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CH2" t="n">
+        <v>6</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>6</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>6</v>
+      </c>
+      <c r="CK2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>214.0292600622386</v>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>160-263</t>
+        </is>
+      </c>
+      <c r="CN2" t="n">
+        <v>316.6666666666487</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>6</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>6</v>
+      </c>
+      <c r="CQ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>234.6019916087851</v>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>201-287</t>
+        </is>
+      </c>
+      <c r="CT2" t="n">
+        <v>333.3333333333144</v>
+      </c>
+      <c r="CU2" t="inlineStr">
         <is>
           <t>tren medido</t>
         </is>
@@ -2693,7 +2801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2712,6 +2820,36 @@
           <t>responde</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_ms</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_medible</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cota_ms</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_ms</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_medible</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_cota_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2723,6 +2861,24 @@
       <c r="C2" t="b">
         <v>1</v>
       </c>
+      <c r="D2" t="n">
+        <v>161.3631978677498</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>299.9999999999829</v>
+      </c>
+      <c r="G2" t="n">
+        <v>283.2028541473245</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>333.3333333333144</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2734,6 +2890,24 @@
       <c r="C3" t="b">
         <v>1</v>
       </c>
+      <c r="D3" t="n">
+        <v>265.9776077166186</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>333.3333333333144</v>
+      </c>
+      <c r="G3" t="n">
+        <v>200.988302697431</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>266.6666666666515</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2745,6 +2919,24 @@
       <c r="C4" t="b">
         <v>1</v>
       </c>
+      <c r="D4" t="n">
+        <v>157.8389678551723</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>299.9999999999829</v>
+      </c>
+      <c r="G4" t="n">
+        <v>290.0808416667828</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>333.3333333333144</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2756,6 +2948,24 @@
       <c r="C5" t="b">
         <v>1</v>
       </c>
+      <c r="D5" t="n">
+        <v>260.0136776866704</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>299.9999999999829</v>
+      </c>
+      <c r="G5" t="n">
+        <v>201.1879243181552</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>366.6666666666458</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2767,6 +2977,24 @@
       <c r="C6" t="b">
         <v>1</v>
       </c>
+      <c r="D6" t="n">
+        <v>199.9988112228356</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>333.3333333333144</v>
+      </c>
+      <c r="G6" t="n">
+        <v>254.0661841492217</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>333.3333333333144</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2777,6 +3005,24 @@
       </c>
       <c r="C7" t="b">
         <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>228.0597089016416</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>333.3333333333144</v>
+      </c>
+      <c r="G7" t="n">
+        <v>215.1377990683486</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>333.3333333333144</v>
       </c>
     </row>
   </sheetData>
